--- a/artfynd/A 30884-2024 artfynd.xlsx
+++ b/artfynd/A 30884-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675954</v>
+        <v>118675955</v>
       </c>
       <c r="B2" t="n">
         <v>78220</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475746</v>
+        <v>475616</v>
       </c>
       <c r="R2" t="n">
-        <v>6847744</v>
+        <v>6847648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675955</v>
+        <v>118675954</v>
       </c>
       <c r="B4" t="n">
         <v>78220</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475616</v>
+        <v>475746</v>
       </c>
       <c r="R4" t="n">
-        <v>6847648</v>
+        <v>6847744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 30884-2024 artfynd.xlsx
+++ b/artfynd/A 30884-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675955</v>
+        <v>118675954</v>
       </c>
       <c r="B2" t="n">
         <v>78220</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475616</v>
+        <v>475746</v>
       </c>
       <c r="R2" t="n">
-        <v>6847648</v>
+        <v>6847744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675954</v>
+        <v>118675955</v>
       </c>
       <c r="B4" t="n">
         <v>78220</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475746</v>
+        <v>475616</v>
       </c>
       <c r="R4" t="n">
-        <v>6847744</v>
+        <v>6847648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 30884-2024 artfynd.xlsx
+++ b/artfynd/A 30884-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675954</v>
+        <v>118675956</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>97770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475746</v>
+        <v>475611</v>
       </c>
       <c r="R2" t="n">
         <v>6847744</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675956</v>
+        <v>118675954</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>78227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475611</v>
+        <v>475746</v>
       </c>
       <c r="R3" t="n">
         <v>6847744</v>
@@ -900,7 +900,7 @@
         <v>118675955</v>
       </c>
       <c r="B4" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30884-2024 artfynd.xlsx
+++ b/artfynd/A 30884-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675954</v>
+        <v>118675955</v>
       </c>
       <c r="B3" t="n">
         <v>78227</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475746</v>
+        <v>475616</v>
       </c>
       <c r="R3" t="n">
-        <v>6847744</v>
+        <v>6847648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675955</v>
+        <v>118675954</v>
       </c>
       <c r="B4" t="n">
         <v>78227</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475616</v>
+        <v>475746</v>
       </c>
       <c r="R4" t="n">
-        <v>6847648</v>
+        <v>6847744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
